--- a/public/plantillas/12_PLAN_SERVICIO_HERRAMIENTAS.xlsx
+++ b/public/plantillas/12_PLAN_SERVICIO_HERRAMIENTAS.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ventura/Desktop/Programacion/recal-hse/public/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C489CCCD-9AD7-5249-B2DD-55045983542A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC075488-D0CA-BE40-969E-3C3F183DB21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3620" yWindow="0" windowWidth="29980" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MTTO DE MAQ" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'MTTO DE MAQ'!$A$1:$L$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'MTTO DE MAQ'!$A$1:$L$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'MTTO DE MAQ'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>DESCRIPCIÓN</t>
   </si>
@@ -53,32 +53,6 @@
   </si>
   <si>
     <t>ELABORÓ</t>
-  </si>
-  <si>
-    <t>OSVALDO JIMENEZ MORALES</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">OBSERVACIONES:                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                                                                     </t>
-    </r>
   </si>
   <si>
     <t>RECAL ESTRUCTURAS
@@ -115,10 +89,30 @@
     <t>CÓDIGO DE INSPECCIÓN *</t>
   </si>
   <si>
-    <t>AUTORIZÓ</t>
+    <t>AUTORIZÓ:</t>
   </si>
   <si>
-    <t>ANTONIO SATURNO FRANCISCO RAMON</t>
+    <r>
+      <t>OBSERVACIONES:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                                                                                                                                     </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -311,7 +305,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -510,11 +504,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -543,6 +618,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -594,20 +708,14 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -663,7 +771,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_16_/+fKaBMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAEcIAAAAAAAAeAUAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAAAAAAAAAAACoAmgMAAAAAAgAAALYD5gCVAgAATQAAAMUVAACHBgAAAQAAADAAAAAUAAAAAAAAAAAA//8AAAEAAAD//wAAAQA="/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_16_/+fKaBMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAEcIAAAAAAAAeAUAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAAAAAAAAAAACoAmgMAAAAAAgAAALYD5gCVAgAATQAAAMUVAACHBgAAAQAAADAAAAAUAAAAAAAAAAAA//8AAAEAAAD//wAAAQA="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -957,7 +1065,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF993"/>
+  <dimension ref="A1:AF994"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -971,80 +1079,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="94.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-    </row>
-    <row r="2" spans="1:32" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="19"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+    </row>
+    <row r="2" spans="1:32" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="32"/>
     </row>
     <row r="3" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="24"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="37"/>
     </row>
     <row r="4" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="27"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="30"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="43"/>
     </row>
     <row r="6" spans="1:32" ht="67.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
@@ -1063,25 +1171,25 @@
         <v>5</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -1113,10 +1221,10 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="9"/>
@@ -1142,21 +1250,19 @@
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:32" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
+    <row r="8" spans="1:32" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="16"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -1178,23 +1284,21 @@
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
     </row>
-    <row r="9" spans="1:32" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="34" t="s">
-        <v>6</v>
+    <row r="9" spans="1:32" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>19</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="23"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1216,33 +1320,64 @@
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
     </row>
-    <row r="10" spans="1:32" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
-        <v>7</v>
+    <row r="10" spans="1:32" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19" t="s">
+        <v>6</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35" t="s">
-        <v>21</v>
+      <c r="E10" s="19"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19" t="s">
+        <v>18</v>
       </c>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-    </row>
-    <row r="11" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+    </row>
+    <row r="11" spans="1:32" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="44"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="46"/>
     </row>
     <row r="12" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
-      <c r="B12" s="11"/>
     </row>
     <row r="13" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
+      <c r="B13" s="11"/>
     </row>
     <row r="14" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
@@ -4184,17 +4319,15 @@
     <row r="993" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2"/>
     </row>
+    <row r="994" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A994" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="4">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:F5"/>
     <mergeCell ref="G3:L5"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="G10:L10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/plantillas/12_PLAN_SERVICIO_HERRAMIENTAS.xlsx
+++ b/public/plantillas/12_PLAN_SERVICIO_HERRAMIENTAS.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ventura/Desktop/Programacion/recal-hse/public/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC075488-D0CA-BE40-969E-3C3F183DB21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F76080-EE4F-0540-8FB3-8A2D0D420464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="0" windowWidth="29980" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MTTO DE MAQ" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'MTTO DE MAQ'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'MTTO DE MAQ'!$A$1:$L$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'MTTO DE MAQ'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -305,7 +305,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -545,19 +545,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -589,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -618,31 +605,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -656,6 +625,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -707,15 +685,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -771,7 +740,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_16_/+fKaBMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAEcIAAAAAAAAeAUAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAAAAAAAAAAACoAmgMAAAAAAgAAALYD5gCVAgAATQAAAMUVAACHBgAAAQAAADAAAAAUAAAAAAAAAAAA//8AAAEAAAD//wAAAQA="/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_16_/+fKaBMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAEcIAAAAAAAAeAUAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAAAAAAAAAAACoAmgMAAAAAAgAAALYD5gCVAgAATQAAAMUVAACHBgAAAQAAADAAAAAUAAAAAAAAAAAA//8AAAEAAAD//wAAAQA="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1065,7 +1034,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF994"/>
+  <dimension ref="A1:AF993"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -1079,80 +1048,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="94.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:32" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="32"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="29"/>
     </row>
     <row r="3" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="37"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="34"/>
     </row>
     <row r="4" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="40"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="37"/>
     </row>
     <row r="5" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="43"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:32" ht="67.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
@@ -1250,19 +1219,21 @@
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:32" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+    <row r="8" spans="1:32" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="15"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="16"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="17"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -1284,21 +1255,23 @@
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
     </row>
-    <row r="9" spans="1:32" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>19</v>
+    <row r="9" spans="1:32" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13" t="s">
+        <v>6</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="23"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="14"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1320,64 +1293,29 @@
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
     </row>
-    <row r="10" spans="1:32" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-    </row>
-    <row r="11" spans="1:32" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="46"/>
+    <row r="10" spans="1:32" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="21"/>
+    </row>
+    <row r="11" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
+      <c r="B12" s="11"/>
     </row>
     <row r="13" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
-      <c r="B13" s="11"/>
     </row>
     <row r="14" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
@@ -4318,9 +4256,6 @@
     </row>
     <row r="993" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2"/>
-    </row>
-    <row r="994" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A994" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
